--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663D9A88-E057-47E2-B19A-7152E42E5FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E109AE6E-290B-4BDC-8CB9-A8007D4DF5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Daily routine</t>
+  </si>
+  <si>
+    <t>fever</t>
   </si>
 </sst>
 </file>
@@ -1331,26 +1334,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>25</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>420</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>165</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E109AE6E-290B-4BDC-8CB9-A8007D4DF5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A153E8F-778B-43CA-9A40-EB6186E006EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>fever</t>
+  </si>
+  <si>
+    <t>something</t>
+  </si>
+  <si>
+    <t>whatever</t>
   </si>
 </sst>
 </file>
@@ -1380,48 +1386,96 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>24</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>390</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1364</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>76</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>400</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A153E8F-778B-43CA-9A40-EB6186E006EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F2D310-E0C4-4713-9863-99F5760F3BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>whatever</t>
+  </si>
+  <si>
+    <t>Nothing</t>
   </si>
 </sst>
 </file>
@@ -1478,26 +1481,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B16" s="14">
+        <v>360</v>
+      </c>
+      <c r="C16" s="14">
+        <v>25</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>45</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>380</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F2D310-E0C4-4713-9863-99F5760F3BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9DCF3A-443F-4956-B3FA-57831611D825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>Nothing</t>
+  </si>
+  <si>
+    <t>good vibes</t>
+  </si>
+  <si>
+    <t>Traveling</t>
   </si>
 </sst>
 </file>
@@ -1527,70 +1533,142 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>25</v>
+      </c>
+      <c r="D17" s="14">
+        <v>110</v>
+      </c>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>340</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>255</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B18" s="14">
+        <v>540</v>
+      </c>
+      <c r="C18" s="14">
+        <v>25</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>700</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1415</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>25</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B19" s="14">
+        <v>540</v>
+      </c>
+      <c r="C19" s="14">
+        <v>25</v>
+      </c>
+      <c r="D19" s="14">
+        <v>50</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>700</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1345</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>95</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9DCF3A-443F-4956-B3FA-57831611D825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FABAA3D-C92A-4B26-BD06-6CCDC0ED04AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,12 @@
   </si>
   <si>
     <t>Traveling</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hactic classes </t>
   </si>
 </sst>
 </file>
@@ -1671,26 +1677,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>25</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>150</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>420</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FABAA3D-C92A-4B26-BD06-6CCDC0ED04AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DBEE3E-DD0F-4E83-8865-09A871F5128E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t xml:space="preserve">hactic classes </t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Mars Test</t>
   </si>
 </sst>
 </file>
@@ -1723,26 +1729,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>80</v>
+      </c>
+      <c r="E21" s="14">
+        <v>80</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>380</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DBEE3E-DD0F-4E83-8865-09A871F5128E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F58294-558F-4908-AD08-9D1C41518506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Mars Test</t>
+  </si>
+  <si>
+    <t>Good days</t>
   </si>
 </sst>
 </file>
@@ -1775,26 +1778,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>61</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>350</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1161</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>279</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F58294-558F-4908-AD08-9D1C41518506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153271CB-2FB7-495F-87D3-62DDC7AEEF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Good days</t>
+  </si>
+  <si>
+    <t>NOTHING</t>
   </si>
 </sst>
 </file>
@@ -1824,26 +1827,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>380</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153271CB-2FB7-495F-87D3-62DDC7AEEF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2CC07D-B553-4514-B1CE-EE6ADB341368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>NOTHING</t>
+  </si>
+  <si>
+    <t>Exam of analyticals</t>
+  </si>
+  <si>
+    <t>Daily vibes</t>
   </si>
 </sst>
 </file>
@@ -1873,48 +1879,96 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>360</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>400</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B25" s="14">
+        <v>540</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>120</v>
+      </c>
+      <c r="G25" s="14">
+        <v>2</v>
+      </c>
+      <c r="H25" s="14">
+        <v>500</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2CC07D-B553-4514-B1CE-EE6ADB341368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1D3D7B-A08F-4436-9344-E2A419DE59B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Daily vibes</t>
+  </si>
+  <si>
+    <t>planning for ca</t>
   </si>
 </sst>
 </file>
@@ -1971,26 +1974,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>20</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>700</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1D3D7B-A08F-4436-9344-E2A419DE59B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D6D0D-4183-488C-A524-CCD28A361C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>planning for ca</t>
+  </si>
+  <si>
+    <t>Traveling and some of concept</t>
   </si>
 </sst>
 </file>
@@ -2020,26 +2023,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>180</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
+        <v>450</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D6D0D-4183-488C-A524-CCD28A361C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF9476A-899F-42A3-BBFD-1A73879FB2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Traveling and some of concept</t>
+  </si>
+  <si>
+    <t>daily vibes</t>
   </si>
 </sst>
 </file>
@@ -2069,26 +2072,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>380</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF9476A-899F-42A3-BBFD-1A73879FB2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E963F3-056C-4EBF-8159-027FFA6F1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2118,26 +2118,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>380</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E963F3-056C-4EBF-8159-027FFA6F1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315C3239-EA3B-4C3F-8AA3-B316CFD8A611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>daily vibes</t>
+  </si>
+  <si>
+    <t>CA Pressure</t>
   </si>
 </sst>
 </file>
@@ -2164,26 +2167,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>380</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315C3239-EA3B-4C3F-8AA3-B316CFD8A611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0D384C-F482-457A-A00C-8F4C4483C9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>CA Pressure</t>
+  </si>
+  <si>
+    <t>Something</t>
   </si>
 </sst>
 </file>
@@ -2213,26 +2216,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>350</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="14">
+        <v>380</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0D384C-F482-457A-A00C-8F4C4483C9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB3B11D-F2BB-4E2F-BCB8-47ECD0EF936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>Something</t>
+  </si>
+  <si>
+    <t>Enjoying the day</t>
+  </si>
+  <si>
+    <t>Nothing just A Normal Day</t>
   </si>
 </sst>
 </file>
@@ -2262,48 +2268,96 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>700</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>750</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB3B11D-F2BB-4E2F-BCB8-47ECD0EF936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD99E6F-53FC-4EB9-AF5B-B7E7EEE87B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>Nothing just A Normal Day</t>
+  </si>
+  <si>
+    <t>Holidays enjoying  because of some unexpected incident.</t>
+  </si>
+  <si>
+    <t>Holidays and preparing for midterm.</t>
   </si>
 </sst>
 </file>
@@ -2359,49 +2365,97 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>240</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>300</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>430</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B35" s="14">
+        <v>540</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>300</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD99E6F-53FC-4EB9-AF5B-B7E7EEE87B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFBE030-41C8-4D04-B182-E7B6716B3D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,18 @@
   </si>
   <si>
     <t>Holidays and preparing for midterm.</t>
+  </si>
+  <si>
+    <t>Travelling for home</t>
+  </si>
+  <si>
+    <t>same reason</t>
+  </si>
+  <si>
+    <t>Good vibess</t>
+  </si>
+  <si>
+    <t>spending time with Parents</t>
   </si>
 </sst>
 </file>
@@ -2458,114 +2470,234 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B36" s="14">
+        <v>540</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>400</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B37" s="14">
+        <v>360</v>
+      </c>
+      <c r="C37" s="14">
+        <v>10</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>20</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>350</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>20</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>350</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>20</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>300</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>20</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFBE030-41C8-4D04-B182-E7B6716B3D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516EDE19-9E7D-45D6-A3B9-B872D741D0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>spending time with Parents</t>
+  </si>
+  <si>
+    <t>Online Classes</t>
   </si>
 </sst>
 </file>
@@ -2700,26 +2703,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>30</v>
+      </c>
+      <c r="F41" s="14">
+        <v>150</v>
+      </c>
+      <c r="G41" s="14">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14">
+        <v>280</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516EDE19-9E7D-45D6-A3B9-B872D741D0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE276FB-F03C-4A04-808C-EC732C597CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2749,48 +2749,96 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>20</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>250</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>280</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>20</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>280</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE276FB-F03C-4A04-808C-EC732C597CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261766CD-3F1F-41CD-8E9E-09D84E1298FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,15 @@
   </si>
   <si>
     <t>Online Classes</t>
+  </si>
+  <si>
+    <t>Travelling to home to University</t>
+  </si>
+  <si>
+    <t>Just a Normal Day</t>
+  </si>
+  <si>
+    <t>On the way</t>
   </si>
 </sst>
 </file>
@@ -2841,70 +2850,142 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>80</v>
+      </c>
+      <c r="E44" s="14">
+        <v>20</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>0</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>900</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>20</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>20</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>500</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>20</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>480</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261766CD-3F1F-41CD-8E9E-09D84E1298FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC140B8-6001-46AC-9A7E-D9B95CFC9338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>On the way</t>
+  </si>
+  <si>
+    <t>Preparing for Exam</t>
+  </si>
+  <si>
+    <t>Exam Day</t>
   </si>
 </sst>
 </file>
@@ -2988,48 +2994,96 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20</v>
+      </c>
+      <c r="D47" s="14">
+        <v>180</v>
+      </c>
+      <c r="E47" s="14">
+        <v>20</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>320</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46338</v>
+      </c>
+      <c r="B48" s="14">
+        <v>360</v>
+      </c>
+      <c r="C48" s="14">
+        <v>20</v>
+      </c>
+      <c r="D48" s="14">
+        <v>180</v>
+      </c>
+      <c r="E48" s="14">
+        <v>20</v>
+      </c>
+      <c r="F48" s="14">
+        <v>120</v>
+      </c>
+      <c r="G48" s="14">
+        <v>2</v>
+      </c>
+      <c r="H48" s="14">
+        <v>420</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC140B8-6001-46AC-9A7E-D9B95CFC9338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EC3C7B-7508-432E-ABE4-2641E491A433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,15 @@
   </si>
   <si>
     <t>Exam Day</t>
+  </si>
+  <si>
+    <t>Exhausted</t>
+  </si>
+  <si>
+    <t>2nd day of exam</t>
+  </si>
+  <si>
+    <t>What a pattern its very shocking</t>
   </si>
 </sst>
 </file>
@@ -3041,7 +3050,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13">
-        <v>46338</v>
+        <v>46307</v>
       </c>
       <c r="B48" s="14">
         <v>360</v>
@@ -3086,70 +3095,142 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B49" s="14">
+        <v>360</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20</v>
+      </c>
+      <c r="D49" s="14">
+        <v>240</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>120</v>
+      </c>
+      <c r="G49" s="14">
+        <v>2</v>
+      </c>
+      <c r="H49" s="14">
+        <v>420</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B50" s="14">
+        <v>280</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20</v>
+      </c>
+      <c r="D50" s="14">
+        <v>220</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>120</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="14">
+        <v>420</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B51" s="14">
+        <v>220</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14">
+        <v>350</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>420</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EC3C7B-7508-432E-ABE4-2641E491A433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940DA3E2-EB58-4BB1-8A94-7CB24BA82EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>What a pattern its very shocking</t>
+  </si>
+  <si>
+    <t>Actually some of personal reason</t>
   </si>
 </sst>
 </file>
@@ -3232,27 +3235,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="14">
+        <v>380</v>
+      </c>
+      <c r="C52" s="14">
+        <v>20</v>
+      </c>
+      <c r="D52" s="14">
+        <v>140</v>
+      </c>
+      <c r="E52" s="14">
+        <v>30</v>
+      </c>
+      <c r="F52" s="14">
+        <v>120</v>
+      </c>
+      <c r="G52" s="14">
+        <v>2</v>
+      </c>
+      <c r="H52" s="14">
+        <v>440</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940DA3E2-EB58-4BB1-8A94-7CB24BA82EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC3D630-79AC-4F24-AA1A-1653F2BC36DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,12 @@
   </si>
   <si>
     <t>Actually some of personal reason</t>
+  </si>
+  <si>
+    <t>Watching the berlin:The Lady of..</t>
+  </si>
+  <si>
+    <t>CA Reevaluation</t>
   </si>
 </sst>
 </file>
@@ -3282,70 +3288,142 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B53" s="14">
+        <v>480</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>140</v>
+      </c>
+      <c r="E53" s="14">
+        <v>30</v>
+      </c>
+      <c r="F53" s="14">
+        <v>120</v>
+      </c>
+      <c r="G53" s="14">
+        <v>2</v>
+      </c>
+      <c r="H53" s="14">
+        <v>360</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+        <v>280</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>30</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>780</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B55" s="14">
+        <v>360</v>
+      </c>
+      <c r="C55" s="14">
+        <v>30</v>
+      </c>
+      <c r="D55" s="14">
+        <v>120</v>
+      </c>
+      <c r="E55" s="14">
+        <v>30</v>
+      </c>
+      <c r="F55" s="14">
+        <v>150</v>
+      </c>
+      <c r="G55" s="14">
+        <v>3</v>
+      </c>
+      <c r="H55" s="14">
+        <v>360</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC3D630-79AC-4F24-AA1A-1653F2BC36DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683D2E01-9393-45A9-9BF1-7659E9F3BBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>CA Reevaluation</t>
+  </si>
+  <si>
+    <t>Enjoying the Dussehera</t>
   </si>
 </sst>
 </file>
@@ -3426,48 +3429,96 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B56" s="14">
+        <v>540</v>
+      </c>
+      <c r="C56" s="14">
+        <v>30</v>
+      </c>
+      <c r="D56" s="14">
+        <v>120</v>
+      </c>
+      <c r="E56" s="14">
+        <v>40</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>360</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B57" s="14">
+        <v>360</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>50</v>
+      </c>
+      <c r="E57" s="14">
+        <v>30</v>
+      </c>
+      <c r="F57" s="14">
+        <v>300</v>
+      </c>
+      <c r="G57" s="14">
+        <v>6</v>
+      </c>
+      <c r="H57" s="14">
+        <v>340</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683D2E01-9393-45A9-9BF1-7659E9F3BBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8019C7F6-35DA-499E-92B2-A27A8867ADBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>Enjoying the Dussehera</t>
+  </si>
+  <si>
+    <t>learning the skills</t>
+  </si>
+  <si>
+    <t>Performing the test</t>
   </si>
 </sst>
 </file>
@@ -3521,48 +3527,96 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B58" s="14">
+        <v>360</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>130</v>
+      </c>
+      <c r="E58" s="14">
+        <v>40</v>
+      </c>
+      <c r="F58" s="14">
+        <v>300</v>
+      </c>
+      <c r="G58" s="14">
+        <v>6</v>
+      </c>
+      <c r="H58" s="14">
+        <v>320</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B59" s="14">
+        <v>360</v>
+      </c>
+      <c r="C59" s="14">
+        <v>30</v>
+      </c>
+      <c r="D59" s="14">
+        <v>120</v>
+      </c>
+      <c r="E59" s="14">
+        <v>20</v>
+      </c>
+      <c r="F59" s="14">
+        <v>300</v>
+      </c>
+      <c r="G59" s="14">
+        <v>6</v>
+      </c>
+      <c r="H59" s="14">
+        <v>340</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8019C7F6-35DA-499E-92B2-A27A8867ADBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0C6661-68A3-4C85-A863-E1FAA2846455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,12 @@
   </si>
   <si>
     <t>Performing the test</t>
+  </si>
+  <si>
+    <t>Same Day</t>
+  </si>
+  <si>
+    <t>Performing Hitbullseye test</t>
   </si>
 </sst>
 </file>
@@ -3619,48 +3625,96 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B60" s="14">
+        <v>490</v>
+      </c>
+      <c r="C60" s="14">
+        <v>30</v>
+      </c>
+      <c r="D60" s="14">
+        <v>180</v>
+      </c>
+      <c r="E60" s="14">
+        <v>45</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>340</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>355</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B61" s="14">
+        <v>540</v>
+      </c>
+      <c r="C61" s="14">
+        <v>20</v>
+      </c>
+      <c r="D61" s="14">
+        <v>240</v>
+      </c>
+      <c r="E61" s="14">
+        <v>30</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>320</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0C6661-68A3-4C85-A863-E1FAA2846455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BEDED8-6118-4D84-826A-B4DC580D1CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Performing Hitbullseye test</t>
+  </si>
+  <si>
+    <t>Same and learning  fundamental</t>
   </si>
 </sst>
 </file>
@@ -3717,26 +3720,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B62" s="14">
+        <v>360</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>120</v>
+      </c>
+      <c r="E62" s="14">
+        <v>30</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>350</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BEDED8-6118-4D84-826A-B4DC580D1CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1B0B67-10EE-4DC3-92BB-51320955FF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,18 @@
   </si>
   <si>
     <t>Same and learning  fundamental</t>
+  </si>
+  <si>
+    <t>Performig good in academics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excited for a new moment </t>
+  </si>
+  <si>
+    <t>having some gossip with friends</t>
+  </si>
+  <si>
+    <t>Unexpected Ca Questions</t>
   </si>
 </sst>
 </file>
@@ -3766,92 +3778,188 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B63" s="14">
+        <v>360</v>
+      </c>
+      <c r="C63" s="14">
+        <v>20</v>
+      </c>
+      <c r="D63" s="14">
+        <v>130</v>
+      </c>
+      <c r="E63" s="14">
+        <v>30</v>
+      </c>
+      <c r="F63" s="14">
+        <v>250</v>
+      </c>
+      <c r="G63" s="14">
+        <v>5</v>
+      </c>
+      <c r="H63" s="14">
+        <v>320</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B64" s="14">
+        <v>360</v>
+      </c>
+      <c r="C64" s="14">
+        <v>20</v>
+      </c>
+      <c r="D64" s="14">
+        <v>120</v>
+      </c>
+      <c r="E64" s="14">
+        <v>40</v>
+      </c>
+      <c r="F64" s="14">
+        <v>300</v>
+      </c>
+      <c r="G64" s="14">
+        <v>6</v>
+      </c>
+      <c r="H64" s="14">
+        <v>320</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B65" s="14">
+        <v>360</v>
+      </c>
+      <c r="C65" s="14">
+        <v>20</v>
+      </c>
+      <c r="D65" s="14">
+        <v>120</v>
+      </c>
+      <c r="E65" s="14">
+        <v>40</v>
+      </c>
+      <c r="F65" s="14">
+        <v>350</v>
+      </c>
+      <c r="G65" s="14">
+        <v>7</v>
+      </c>
+      <c r="H65" s="14">
+        <v>320</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B66" s="14">
+        <v>360</v>
+      </c>
+      <c r="C66" s="14">
+        <v>20</v>
+      </c>
+      <c r="D66" s="14">
+        <v>130</v>
+      </c>
+      <c r="E66" s="14">
+        <v>40</v>
+      </c>
+      <c r="F66" s="14">
+        <v>300</v>
+      </c>
+      <c r="G66" s="14">
+        <v>5</v>
+      </c>
+      <c r="H66" s="14">
+        <v>320</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
